--- a/research/brics_universities/output/BRICS_universities_India.xlsx
+++ b/research/brics_universities/output/BRICS_universities_India.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Индия" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Волна 1'!$A$1:$AI$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Волна 1'!$A$1:$AI$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Индия'!$A$1:$AI$201</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -482,7 +482,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Дата формирования: 2026-10-02</t>
+          <t>Дата формирования: 2026-10-04</t>
         </is>
       </c>
     </row>
@@ -538,13 +538,13 @@
         <v>200</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F5" t="n">
         <v>156</v>
@@ -580,7 +580,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Волна 1A: есть запущенные КА и индекс ≥ 60. Волна 1B: новые члены БРИКС+ и ключевые точки для наземных станций (индекс ≥ 40).</t>
+          <t>Волна 1A: у вуза есть собственные запущенные КА. Волна 1B: новые члены БРИКС+ и ключевые точки для наземных станций (индекс ≥ 40).</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI11"/>
+  <dimension ref="A1:AI15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="AH2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI2" s="4" t="inlineStr"/>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="AH3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI3" s="4" t="inlineStr"/>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AH4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI4" s="4" t="inlineStr"/>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="AH5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI5" s="4" t="inlineStr"/>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="AH6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI6" s="4" t="inlineStr"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="AH7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI7" s="4" t="inlineStr"/>
@@ -2076,7 +2076,7 @@
       </c>
       <c r="AH8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI8" s="4" t="inlineStr"/>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AH9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI9" s="4" t="inlineStr"/>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="AH10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI10" s="4" t="inlineStr"/>
@@ -2577,13 +2577,613 @@
       </c>
       <c r="AH11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI11" s="4" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Индия</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Нагпур</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>G H Raisoni College of Engineering</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Технический / аэрокосмический</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Частный</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>• Engineering
+• Computer Science &amp; IT
+• Electronics
+• Electrical Engineering
+• Management (MBA)</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>G H Raisoni College of Engineering, CRPF Gate No. 3, Hingna Road, Digdoh Hills, Nagpur, Maharashtra 440016, India</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>principal.ghrce@raisoni.net</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>Dr. Sachin Untawale
+Директор колледжа
+Офис директора колледжа (Director / Principal, GHRCE)
+Обращение: Dear Dr. Untawale,</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr"/>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>principal.ghrce@raisoni.net</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>+91-7104-232560</t>
+        </is>
+      </c>
+      <c r="O12" s="4" t="inlineStr">
+        <is>
+          <t>https://ghrce.raisoni.net</t>
+        </is>
+      </c>
+      <c r="P12" s="4" t="inlineStr">
+        <is>
+          <t>Dr. Sachin Untawale</t>
+        </is>
+      </c>
+      <c r="Q12" s="4" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="R12" s="4" t="inlineStr"/>
+      <c r="S12" s="4" t="inlineStr"/>
+      <c r="T12" s="4" t="inlineStr"/>
+      <c r="U12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" s="4" t="inlineStr">
+        <is>
+          <t>GHRCEsat / UNITYsat-2 (2021)</t>
+        </is>
+      </c>
+      <c r="W12" s="4" t="inlineStr"/>
+      <c r="X12" s="4" t="inlineStr"/>
+      <c r="Y12" s="4" t="inlineStr">
+        <is>
+          <t>• Students' Nano-Satellite team
+• Centre of Excellence in Astrophysics and Cosmology</t>
+        </is>
+      </c>
+      <c r="Z12" s="4" t="inlineStr">
+        <is>
+          <t>• ISRO — launch of GHRCEsat (UNITYsat) on PSLV-C51 (28.02.2021)
+• Indian Technology Congress Association (ITCA) — MoU of 26.10.2018 on student satellite development (UNITYsat programme)</t>
+        </is>
+      </c>
+      <c r="AA12" s="4" t="inlineStr"/>
+      <c r="AB12" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AC12" s="5" t="inlineStr">
+        <is>
+          <t>1A</t>
+        </is>
+      </c>
+      <c r="AD12" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="AE12" s="4" t="inlineStr">
+        <is>
+          <t>средняя</t>
+        </is>
+      </c>
+      <c r="AF12" s="4" t="inlineStr">
+        <is>
+          <t>• Автономный частный колледж (Raisoni Group), аффилирован с RTM Nagpur University; в NIRF 2025 не ранжирован (в 2024 — 163 место, инженерия)
+• GHRCEsat — 0,25U пико-спутник в составе UNITYsat (совместно с JIT и SSIET), запущен PSLV-C51 28.02.2021, сошёл с орбиты; в nanosats.eu организация ошибочно указана как G H Raisoni Institute of Engineering and Technology
+• Отдельного e-mail международного офиса не опубликовано; указан e-mail директора/principal
+• Сайт — SPA на Angular, данные извлечены из JS-бандла сайта; есть International Relations Office, IR Officer — Dr Bhakti Rajvaidya (e-mail не опубликован)</t>
+        </is>
+      </c>
+      <c r="AG12" s="4" t="inlineStr">
+        <is>
+          <t>• Https://ghrce.raisoni.net/
+• Https://ghrce.raisoni.net/contact
+• Https://www.isro.gov.in/UNITYSAT.html
+• Https://www.isro.gov.in/StudentSatellite.html
+• Https://en.wikipedia.org/wiki/G._H._Raisoni_College_of_Engineering_Nagpur
+• Nanosats.eu (UNITYSat 2)</t>
+        </is>
+      </c>
+      <c r="AH12" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AI12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Индия</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Шриперумбудур (Ченнаи)</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Jeppiaar Institute of Technology</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>ஜேப்பியார் தொழில்நுட்பக் கல்லூரி</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Технический / аэрокосмический</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>Частный</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>• Computer Science and Engineering
+• Information Technology
+• Electronics and Communication Engineering
+• Mechanical Engineering
+• Artificial Intelligence and Data Science
+• Business Administration</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>Jeppiaar Institute of Technology, Kunnam, Sunguvarchatram, Sriperumbudur (TK), Chennai - 631 604, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>principal@jeppiaarinstitute.org</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>Dr. J. Venu Gopala Krishnan
+Директор колледжа (Principal)
+Офис директора колледжа (Principal's Office)
+Обращение: Dear Dr. Venu Gopala Krishnan,</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr"/>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>principal@jeppiaarinstitute.org</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>+91-44-27159000</t>
+        </is>
+      </c>
+      <c r="O13" s="4" t="inlineStr">
+        <is>
+          <t>https://www.jeppiaarinstitute.org</t>
+        </is>
+      </c>
+      <c r="P13" s="4" t="inlineStr">
+        <is>
+          <t>Dr. J. Venu Gopala Krishnan</t>
+        </is>
+      </c>
+      <c r="Q13" s="4" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="R13" s="4" t="inlineStr"/>
+      <c r="S13" s="4" t="inlineStr"/>
+      <c r="T13" s="4" t="inlineStr"/>
+      <c r="U13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" s="4" t="inlineStr">
+        <is>
+          <t>JITsat / UNITYsat-1 (2021)</t>
+        </is>
+      </c>
+      <c r="W13" s="4" t="inlineStr"/>
+      <c r="X13" s="4" t="inlineStr"/>
+      <c r="Y13" s="4" t="inlineStr"/>
+      <c r="Z13" s="4" t="inlineStr">
+        <is>
+          <t>ISRO / NSIL (launch of UNITYsat on PSLV-C51)</t>
+        </is>
+      </c>
+      <c r="AA13" s="4" t="inlineStr"/>
+      <c r="AB13" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="AC13" s="5" t="inlineStr">
+        <is>
+          <t>1A</t>
+        </is>
+      </c>
+      <c r="AD13" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="AE13" s="4" t="inlineStr">
+        <is>
+          <t>средняя</t>
+        </is>
+      </c>
+      <c r="AF13" s="4" t="inlineStr">
+        <is>
+          <t>• Частный самофинансируемый колледж (основан в 2011 г.), не университет; аффилирован с Anna University (по общим сведениям, на сайте не перепроверено)
+• JITsat запущен 28.02.2021 на PSLV-C51 в составе UNITYsat вместе с GHRCE (Нагпур) и Sri Shakthi IET (Коимбатур); по nanosats.eu — сошёл с орбиты, сигнала не было
+• Отдельного международного офиса нет; писать на адрес директора колледжа (principal@); общий адрес — office@jeppiaarinstitute.org
+• Страница Principal Desk при проверке не открывалась; имя директора подтверждено на странице Executive Members</t>
+        </is>
+      </c>
+      <c r="AG13" s="4" t="inlineStr">
+        <is>
+          <t>• Https://www.jeppiaarinstitute.org/contact/
+• Https://www.jeppiaarinstitute.org/executive-members/
+• Https://www.jeppiaarinstitute.org/management/
+• Https://www.isro.gov.in/mission_PSLV_C51_UNITYsat.html
+• Nanosats.eu (UNITYSat 1 / JITSat)</t>
+        </is>
+      </c>
+      <c r="AH13" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AI13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Индия</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Бангалор</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>M. S. Ramaiah Institute of Technology</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Ramaiah Institute of Technology (RIT; formerly M. S. Ramaiah Institute of Technology)</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Технический / аэрокосмический</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>Частный</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>• Computer Science
+• Electronics &amp; Communication
+• Mechanical Engineering
+• Civil Engineering
+• Electrical Engineering
+• Architecture</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>Ramaiah Institute of Technology, MSR Nagar, MSRIT Post, Bengaluru 560054, Karnataka, India</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>principal@msrit.edu</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>Dr. B. Sathish Babu
+Директор колледжа (Principal)
+Канцелярия директора колледжа (Office of the Principal)
+Обращение: Dear Dr. Sathish Babu,</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr"/>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>principal@msrit.edu</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>+91 80 2360 0822</t>
+        </is>
+      </c>
+      <c r="O14" s="4" t="inlineStr">
+        <is>
+          <t>https://www.msrit.edu</t>
+        </is>
+      </c>
+      <c r="P14" s="4" t="inlineStr">
+        <is>
+          <t>Dr. B. Sathish Babu</t>
+        </is>
+      </c>
+      <c r="Q14" s="4" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="R14" s="4" t="inlineStr"/>
+      <c r="S14" s="4" t="inlineStr"/>
+      <c r="T14" s="4" t="inlineStr">
+        <is>
+          <t>NIRF2025 Engineering: 75</t>
+        </is>
+      </c>
+      <c r="U14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" s="4" t="inlineStr">
+        <is>
+          <t>STUDSAT (2010, co-built in a 7-college consortium led by NMIT)</t>
+        </is>
+      </c>
+      <c r="W14" s="4" t="inlineStr"/>
+      <c r="X14" s="4" t="inlineStr"/>
+      <c r="Y14" s="4" t="inlineStr"/>
+      <c r="Z14" s="4" t="inlineStr">
+        <is>
+          <t>ISRO (STUDSAT launched on PSLV-C15)</t>
+        </is>
+      </c>
+      <c r="AA14" s="4" t="inlineStr"/>
+      <c r="AB14" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="AC14" s="5" t="inlineStr">
+        <is>
+          <t>1A</t>
+        </is>
+      </c>
+      <c r="AD14" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="AE14" s="4" t="inlineStr">
+        <is>
+          <t>средняя</t>
+        </is>
+      </c>
+      <c r="AF14" s="4" t="inlineStr">
+        <is>
+          <t>• Автономный частный колледж, аффилированный с VTU (не университет); глава — Principal
+• Участник консорциума STUDSAT (первый студенческий пикоспутник Индии, PSLV-C15, 12.07.2010) — по Википедии; вклад RIT, вероятно, частичный
+• Офиса международных связей на сайте не найдено
+• STUDSAT (2010) — участие в консорциуме из 7 колледжей; головной исполнитель — NMIT</t>
+        </is>
+      </c>
+      <c r="AG14" s="4" t="inlineStr">
+        <is>
+          <t>• Https://www.msrit.edu/contact-us.html
+• Https://www.msrit.edu/gb/principal.html
+• Https://en.wikipedia.org/wiki/StudSat
+• Https://www.isro.gov.in/StudentSatellite.html</t>
+        </is>
+      </c>
+      <c r="AH14" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AI14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Индия</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Коимбатур</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Sri Shakthi Institute of Engineering and Technology</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>ஸ்ரீ சக்தி இன்ஸ்டிடியூட் ஆஃப் இன்ஜினியரிங் அண்ட் டெக்னாலஜி</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Технический / аэрокосмический</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>Частный</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>• Engineering
+• Computer Science
+• Electronics &amp; Communication
+• Mechanical Engineering
+• Information Technology</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>Sri Shakthi Nagar, L &amp; T By-Pass, Chinniyampalayam Post, Coimbatore 641062, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>principal@siet.ac.in</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>Dr. N. K. Sakthivel
+Принципал (руководитель института)
+Офис принципала (Principal's Office)
+Обращение: Dear Dr. Sakthivel,</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr"/>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>principal@siet.ac.in</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>+91 422 2369900</t>
+        </is>
+      </c>
+      <c r="O15" s="4" t="inlineStr">
+        <is>
+          <t>https://www.siet.ac.in</t>
+        </is>
+      </c>
+      <c r="P15" s="4" t="inlineStr">
+        <is>
+          <t>Dr. N. K. Sakthivel</t>
+        </is>
+      </c>
+      <c r="Q15" s="4" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="R15" s="4" t="inlineStr"/>
+      <c r="S15" s="4" t="inlineStr"/>
+      <c r="T15" s="4" t="inlineStr"/>
+      <c r="U15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" s="4" t="inlineStr">
+        <is>
+          <t>Sri Shakthi Sat (UNITYsat, 2021)</t>
+        </is>
+      </c>
+      <c r="W15" s="4" t="inlineStr"/>
+      <c r="X15" s="4" t="inlineStr"/>
+      <c r="Y15" s="4" t="inlineStr"/>
+      <c r="Z15" s="4" t="inlineStr"/>
+      <c r="AA15" s="4" t="inlineStr"/>
+      <c r="AB15" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="AC15" s="5" t="inlineStr">
+        <is>
+          <t>1A</t>
+        </is>
+      </c>
+      <c r="AD15" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="AE15" s="4" t="inlineStr">
+        <is>
+          <t>средняя</t>
+        </is>
+      </c>
+      <c r="AF15" s="4" t="inlineStr">
+        <is>
+          <t>• Сайт siet.ac.in закрыт Cloudflare (403) — контакты и имя принципала взяты из поисковой выдачи по официальным страницам, требуют перепроверки
+• Автономный частный колледж, аффилирован с Anna University (не университет); председатель — S. Thangavelu (Wikipedia)
+• Sri Shakthi Sat — один из трёх студенческих спутников кластера UNITYsat (с JIT Шрипермбудур и GHRCE Нагпур), запущен PSLV-C51 28.02.2021; по nanosats.csv — сошёл с орбиты, сигнала нет
+• Отдельного международного офиса не найдено; писать принципалу. Общая почта также info@siet.ac.in</t>
+        </is>
+      </c>
+      <c r="AG15" s="4" t="inlineStr">
+        <is>
+          <t>• Https://www.siet.ac.in/contact-us
+• Https://www.siet.ac.in/from-the-principal
+• Https://en.wikipedia.org/wiki/Sri_Shakthi_Institute_of_Engineering_and_Technology
+• Https://www.isro.gov.in/mission_PSLV_C51_UNITYsat.html
+• Nanosats.csv (UNITYSat 3)</t>
+        </is>
+      </c>
+      <c r="AH15" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AI15" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AI11"/>
+  <autoFilter ref="A1:AI15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2984,7 +3584,7 @@
       </c>
       <c r="AH2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI2" s="4" t="inlineStr"/>
@@ -3151,7 +3751,7 @@
       </c>
       <c r="AH3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI3" s="4" t="inlineStr"/>
@@ -3328,7 +3928,7 @@
       </c>
       <c r="AH4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI4" s="4" t="inlineStr"/>
@@ -3493,7 +4093,7 @@
       </c>
       <c r="AH5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI5" s="4" t="inlineStr"/>
@@ -3678,7 +4278,7 @@
       </c>
       <c r="AH6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI6" s="4" t="inlineStr"/>
@@ -3852,7 +4452,7 @@
       </c>
       <c r="AH7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI7" s="4" t="inlineStr"/>
@@ -4026,7 +4626,7 @@
       </c>
       <c r="AH8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI8" s="4" t="inlineStr"/>
@@ -4203,7 +4803,7 @@
       </c>
       <c r="AH9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI9" s="4" t="inlineStr"/>
@@ -4366,7 +4966,7 @@
       </c>
       <c r="AH10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI10" s="4" t="inlineStr"/>
@@ -4527,7 +5127,7 @@
       </c>
       <c r="AH11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI11" s="4" t="inlineStr"/>
@@ -4706,7 +5306,7 @@
       </c>
       <c r="AH12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI12" s="4" t="inlineStr"/>
@@ -4888,7 +5488,7 @@
       </c>
       <c r="AH13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI13" s="4" t="inlineStr"/>
@@ -5057,7 +5657,7 @@
       </c>
       <c r="AH14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI14" s="4" t="inlineStr"/>
@@ -5229,7 +5829,7 @@
       </c>
       <c r="AH15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI15" s="4" t="inlineStr"/>
@@ -5346,9 +5946,9 @@
       <c r="AB16" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="AC16" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
+      <c r="AC16" s="5" t="inlineStr">
+        <is>
+          <t>1A</t>
         </is>
       </c>
       <c r="AD16" s="4" t="inlineStr">
@@ -5381,7 +5981,7 @@
       </c>
       <c r="AH16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI16" s="4" t="inlineStr"/>
@@ -5544,7 +6144,7 @@
       </c>
       <c r="AH17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI17" s="4" t="inlineStr"/>
@@ -5713,7 +6313,7 @@
       </c>
       <c r="AH18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI18" s="4" t="inlineStr"/>
@@ -5886,7 +6486,7 @@
       </c>
       <c r="AH19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI19" s="4" t="inlineStr"/>
@@ -6061,7 +6661,7 @@
       </c>
       <c r="AH20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI20" s="4" t="inlineStr"/>
@@ -6177,9 +6777,9 @@
       <c r="AB21" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="AC21" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
+      <c r="AC21" s="5" t="inlineStr">
+        <is>
+          <t>1A</t>
         </is>
       </c>
       <c r="AD21" s="4" t="inlineStr">
@@ -6211,7 +6811,7 @@
       </c>
       <c r="AH21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI21" s="4" t="inlineStr"/>
@@ -6331,9 +6931,9 @@
       <c r="AB22" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="AC22" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
+      <c r="AC22" s="5" t="inlineStr">
+        <is>
+          <t>1A</t>
         </is>
       </c>
       <c r="AD22" s="4" t="inlineStr">
@@ -6364,7 +6964,7 @@
       </c>
       <c r="AH22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI22" s="4" t="inlineStr"/>
@@ -6533,7 +7133,7 @@
       </c>
       <c r="AH23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI23" s="4" t="inlineStr"/>
@@ -6686,7 +7286,7 @@
       </c>
       <c r="AH24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI24" s="4" t="inlineStr"/>
@@ -6845,7 +7445,7 @@
       </c>
       <c r="AH25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI25" s="4" t="inlineStr"/>
@@ -7006,7 +7606,7 @@
       </c>
       <c r="AH26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI26" s="4" t="inlineStr"/>
@@ -7168,7 +7768,7 @@
       </c>
       <c r="AH27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI27" s="4" t="inlineStr"/>
@@ -7337,7 +7937,7 @@
       </c>
       <c r="AH28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI28" s="4" t="inlineStr"/>
@@ -7504,7 +8104,7 @@
       </c>
       <c r="AH29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI29" s="4" t="inlineStr"/>
@@ -7669,7 +8269,7 @@
       </c>
       <c r="AH30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI30" s="4" t="inlineStr"/>
@@ -7827,7 +8427,7 @@
       </c>
       <c r="AH31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI31" s="4" t="inlineStr"/>
@@ -7938,9 +8538,9 @@
       <c r="AB32" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="AC32" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
+      <c r="AC32" s="5" t="inlineStr">
+        <is>
+          <t>1A</t>
         </is>
       </c>
       <c r="AD32" s="4" t="inlineStr">
@@ -7972,7 +8572,7 @@
       </c>
       <c r="AH32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI32" s="4" t="inlineStr"/>
@@ -8123,7 +8723,7 @@
       </c>
       <c r="AH33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI33" s="4" t="inlineStr"/>
@@ -8289,7 +8889,7 @@
       </c>
       <c r="AH34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI34" s="4" t="inlineStr"/>
@@ -8451,7 +9051,7 @@
       </c>
       <c r="AH35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI35" s="4" t="inlineStr"/>
@@ -8609,7 +9209,7 @@
       </c>
       <c r="AH36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI36" s="4" t="inlineStr"/>
@@ -8767,7 +9367,7 @@
       </c>
       <c r="AH37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI37" s="4" t="inlineStr"/>
@@ -8915,7 +9515,7 @@
       </c>
       <c r="AH38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI38" s="4" t="inlineStr"/>
@@ -9066,7 +9666,7 @@
       </c>
       <c r="AH39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI39" s="4" t="inlineStr"/>
@@ -9224,7 +9824,7 @@
       </c>
       <c r="AH40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI40" s="4" t="inlineStr"/>
@@ -9374,7 +9974,7 @@
       </c>
       <c r="AH41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI41" s="4" t="inlineStr"/>
@@ -9515,7 +10115,7 @@
       </c>
       <c r="AH42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI42" s="4" t="inlineStr"/>
@@ -9663,7 +10263,7 @@
       </c>
       <c r="AH43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI43" s="4" t="inlineStr"/>
@@ -9819,7 +10419,7 @@
       </c>
       <c r="AH44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI44" s="4" t="inlineStr"/>
@@ -9976,7 +10576,7 @@
       </c>
       <c r="AH45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI45" s="4" t="inlineStr"/>
@@ -10130,7 +10730,7 @@
       </c>
       <c r="AH46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI46" s="4" t="inlineStr"/>
@@ -10271,7 +10871,7 @@
       </c>
       <c r="AH47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI47" s="4" t="inlineStr"/>
@@ -10424,7 +11024,7 @@
       </c>
       <c r="AH48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI48" s="4" t="inlineStr"/>
@@ -10580,7 +11180,7 @@
       </c>
       <c r="AH49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI49" s="4" t="inlineStr"/>
@@ -10740,7 +11340,7 @@
       </c>
       <c r="AH50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI50" s="4" t="inlineStr"/>
@@ -10894,7 +11494,7 @@
       </c>
       <c r="AH51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI51" s="4" t="inlineStr"/>
@@ -11042,7 +11642,7 @@
       </c>
       <c r="AH52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI52" s="4" t="inlineStr"/>
@@ -11196,7 +11796,7 @@
       </c>
       <c r="AH53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI53" s="4" t="inlineStr"/>
@@ -11349,7 +11949,7 @@
       </c>
       <c r="AH54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI54" s="4" t="inlineStr"/>
@@ -11500,7 +12100,7 @@
       </c>
       <c r="AH55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI55" s="4" t="inlineStr"/>
@@ -11654,7 +12254,7 @@
       </c>
       <c r="AH56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI56" s="4" t="inlineStr"/>
@@ -11804,7 +12404,7 @@
       </c>
       <c r="AH57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI57" s="4" t="inlineStr"/>
@@ -11954,7 +12554,7 @@
       </c>
       <c r="AH58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI58" s="4" t="inlineStr"/>
@@ -12099,7 +12699,7 @@
       </c>
       <c r="AH59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI59" s="4" t="inlineStr"/>
@@ -12248,7 +12848,7 @@
       </c>
       <c r="AH60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI60" s="4" t="inlineStr"/>
@@ -12401,7 +13001,7 @@
       </c>
       <c r="AH61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI61" s="4" t="inlineStr"/>
@@ -12556,7 +13156,7 @@
       </c>
       <c r="AH62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI62" s="4" t="inlineStr"/>
@@ -12703,7 +13303,7 @@
       </c>
       <c r="AH63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI63" s="4" t="inlineStr"/>
@@ -12853,7 +13453,7 @@
       </c>
       <c r="AH64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI64" s="4" t="inlineStr"/>
@@ -13003,7 +13603,7 @@
       </c>
       <c r="AH65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI65" s="4" t="inlineStr"/>
@@ -13156,7 +13756,7 @@
       </c>
       <c r="AH66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI66" s="4" t="inlineStr"/>
@@ -13315,7 +13915,7 @@
       </c>
       <c r="AH67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI67" s="4" t="inlineStr"/>
@@ -13469,7 +14069,7 @@
       </c>
       <c r="AH68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI68" s="4" t="inlineStr"/>
@@ -13624,7 +14224,7 @@
       </c>
       <c r="AH69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI69" s="4" t="inlineStr"/>
@@ -13780,7 +14380,7 @@
       </c>
       <c r="AH70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI70" s="4" t="inlineStr"/>
@@ -13932,7 +14532,7 @@
       </c>
       <c r="AH71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI71" s="4" t="inlineStr"/>
@@ -14084,7 +14684,7 @@
       </c>
       <c r="AH72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI72" s="4" t="inlineStr"/>
@@ -14237,7 +14837,7 @@
       </c>
       <c r="AH73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI73" s="4" t="inlineStr"/>
@@ -14386,7 +14986,7 @@
       </c>
       <c r="AH74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI74" s="4" t="inlineStr"/>
@@ -14538,7 +15138,7 @@
       </c>
       <c r="AH75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI75" s="4" t="inlineStr"/>
@@ -14692,7 +15292,7 @@
       </c>
       <c r="AH76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI76" s="4" t="inlineStr"/>
@@ -14841,7 +15441,7 @@
       </c>
       <c r="AH77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI77" s="4" t="inlineStr"/>
@@ -14989,7 +15589,7 @@
       </c>
       <c r="AH78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI78" s="4" t="inlineStr"/>
@@ -15138,7 +15738,7 @@
       </c>
       <c r="AH79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI79" s="4" t="inlineStr"/>
@@ -15282,7 +15882,7 @@
       </c>
       <c r="AH80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI80" s="4" t="inlineStr"/>
@@ -15404,7 +16004,7 @@
       </c>
       <c r="AH81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI81" s="4" t="inlineStr"/>
@@ -15557,7 +16157,7 @@
       </c>
       <c r="AH82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI82" s="4" t="inlineStr"/>
@@ -15709,7 +16309,7 @@
       </c>
       <c r="AH83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI83" s="4" t="inlineStr"/>
@@ -15860,7 +16460,7 @@
       </c>
       <c r="AH84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI84" s="4" t="inlineStr"/>
@@ -16010,7 +16610,7 @@
       </c>
       <c r="AH85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI85" s="4" t="inlineStr"/>
@@ -16153,7 +16753,7 @@
       </c>
       <c r="AH86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI86" s="4" t="inlineStr"/>
@@ -16302,7 +16902,7 @@
       </c>
       <c r="AH87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI87" s="4" t="inlineStr"/>
@@ -16456,7 +17056,7 @@
       </c>
       <c r="AH88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI88" s="4" t="inlineStr"/>
@@ -16609,7 +17209,7 @@
       </c>
       <c r="AH89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI89" s="4" t="inlineStr"/>
@@ -16751,7 +17351,7 @@
       </c>
       <c r="AH90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI90" s="4" t="inlineStr"/>
@@ -16901,7 +17501,7 @@
       </c>
       <c r="AH91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI91" s="4" t="inlineStr"/>
@@ -17006,7 +17606,7 @@
       </c>
       <c r="AH92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI92" s="4" t="inlineStr"/>
@@ -17129,7 +17729,7 @@
       </c>
       <c r="AD93" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="AE93" s="4" t="inlineStr">
@@ -17153,7 +17753,7 @@
       </c>
       <c r="AH93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI93" s="4" t="inlineStr"/>
@@ -17308,7 +17908,7 @@
       </c>
       <c r="AH94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI94" s="4" t="inlineStr"/>
@@ -17457,7 +18057,7 @@
       </c>
       <c r="AH95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI95" s="4" t="inlineStr"/>
@@ -17609,7 +18209,7 @@
       </c>
       <c r="AH96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI96" s="4" t="inlineStr"/>
@@ -17762,7 +18362,7 @@
       </c>
       <c r="AH97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI97" s="4" t="inlineStr"/>
@@ -17901,7 +18501,7 @@
       </c>
       <c r="AH98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI98" s="4" t="inlineStr"/>
@@ -18028,7 +18628,7 @@
       </c>
       <c r="AD99" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="AE99" s="4" t="inlineStr">
@@ -18052,7 +18652,7 @@
       </c>
       <c r="AH99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI99" s="4" t="inlineStr"/>
@@ -18205,7 +18805,7 @@
       </c>
       <c r="AH100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI100" s="4" t="inlineStr"/>
@@ -18354,7 +18954,7 @@
       </c>
       <c r="AH101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI101" s="4" t="inlineStr"/>
@@ -18507,7 +19107,7 @@
       </c>
       <c r="AH102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI102" s="4" t="inlineStr"/>
@@ -18657,7 +19257,7 @@
       </c>
       <c r="AH103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI103" s="4" t="inlineStr"/>
@@ -18812,7 +19412,7 @@
       </c>
       <c r="AH104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI104" s="4" t="inlineStr"/>
@@ -18963,7 +19563,7 @@
       </c>
       <c r="AH105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI105" s="4" t="inlineStr"/>
@@ -19109,7 +19709,7 @@
       </c>
       <c r="AH106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI106" s="4" t="inlineStr"/>
@@ -19257,7 +19857,7 @@
       </c>
       <c r="AH107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI107" s="4" t="inlineStr"/>
@@ -19395,7 +19995,7 @@
       </c>
       <c r="AH108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI108" s="4" t="inlineStr"/>
@@ -19542,7 +20142,7 @@
       </c>
       <c r="AH109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI109" s="4" t="inlineStr"/>
@@ -19691,7 +20291,7 @@
       </c>
       <c r="AH110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI110" s="4" t="inlineStr"/>
@@ -19829,7 +20429,7 @@
       </c>
       <c r="AH111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI111" s="4" t="inlineStr"/>
@@ -19972,7 +20572,7 @@
       </c>
       <c r="AH112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI112" s="4" t="inlineStr"/>
@@ -20120,7 +20720,7 @@
       </c>
       <c r="AH113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI113" s="4" t="inlineStr"/>
@@ -20266,7 +20866,7 @@
       </c>
       <c r="AH114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI114" s="4" t="inlineStr"/>
@@ -20413,7 +21013,7 @@
       </c>
       <c r="AH115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI115" s="4" t="inlineStr"/>
@@ -20557,7 +21157,7 @@
       </c>
       <c r="AH116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI116" s="4" t="inlineStr"/>
@@ -20700,7 +21300,7 @@
       </c>
       <c r="AH117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI117" s="4" t="inlineStr"/>
@@ -20845,7 +21445,7 @@
       </c>
       <c r="AH118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI118" s="4" t="inlineStr"/>
@@ -20987,7 +21587,7 @@
       </c>
       <c r="AH119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI119" s="4" t="inlineStr"/>
@@ -21130,7 +21730,7 @@
       </c>
       <c r="AH120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI120" s="4" t="inlineStr"/>
@@ -21273,7 +21873,7 @@
       </c>
       <c r="AH121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI121" s="4" t="inlineStr"/>
@@ -21416,7 +22016,7 @@
       </c>
       <c r="AH122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI122" s="4" t="inlineStr"/>
@@ -21560,7 +22160,7 @@
       </c>
       <c r="AH123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI123" s="4" t="inlineStr"/>
@@ -21668,7 +22268,7 @@
       </c>
       <c r="AH124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI124" s="4" t="inlineStr"/>
@@ -21804,7 +22404,7 @@
       </c>
       <c r="AH125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI125" s="4" t="inlineStr"/>
@@ -21946,7 +22546,7 @@
       </c>
       <c r="AH126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI126" s="4" t="inlineStr"/>
@@ -22061,7 +22661,7 @@
       </c>
       <c r="AH127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI127" s="4" t="inlineStr"/>
@@ -22180,7 +22780,7 @@
       </c>
       <c r="AH128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI128" s="4" t="inlineStr"/>
@@ -22333,7 +22933,7 @@
       </c>
       <c r="AH129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI129" s="4" t="inlineStr"/>
@@ -22485,7 +23085,7 @@
       </c>
       <c r="AH130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI130" s="4" t="inlineStr"/>
@@ -22634,7 +23234,7 @@
       </c>
       <c r="AH131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI131" s="4" t="inlineStr"/>
@@ -22787,7 +23387,7 @@
       </c>
       <c r="AH132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI132" s="4" t="inlineStr"/>
@@ -22902,7 +23502,7 @@
       </c>
       <c r="AH133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI133" s="4" t="inlineStr"/>
@@ -23055,7 +23655,7 @@
       </c>
       <c r="AH134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI134" s="4" t="inlineStr"/>
@@ -23209,7 +23809,7 @@
       </c>
       <c r="AH135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI135" s="4" t="inlineStr"/>
@@ -23362,7 +23962,7 @@
       </c>
       <c r="AH136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI136" s="4" t="inlineStr"/>
@@ -23508,7 +24108,7 @@
       </c>
       <c r="AH137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI137" s="4" t="inlineStr"/>
@@ -23657,7 +24257,7 @@
       </c>
       <c r="AH138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI138" s="4" t="inlineStr"/>
@@ -23805,7 +24405,7 @@
       </c>
       <c r="AH139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI139" s="4" t="inlineStr"/>
@@ -23951,7 +24551,7 @@
       </c>
       <c r="AH140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI140" s="4" t="inlineStr"/>
@@ -24103,7 +24703,7 @@
       </c>
       <c r="AH141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI141" s="4" t="inlineStr"/>
@@ -24248,7 +24848,7 @@
       </c>
       <c r="AH142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI142" s="4" t="inlineStr"/>
@@ -24395,7 +24995,7 @@
       </c>
       <c r="AH143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI143" s="4" t="inlineStr"/>
@@ -24537,7 +25137,7 @@
       </c>
       <c r="AH144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI144" s="4" t="inlineStr"/>
@@ -24683,7 +25283,7 @@
       </c>
       <c r="AH145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI145" s="4" t="inlineStr"/>
@@ -24827,7 +25427,7 @@
       </c>
       <c r="AH146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI146" s="4" t="inlineStr"/>
@@ -24979,7 +25579,7 @@
       </c>
       <c r="AH147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI147" s="4" t="inlineStr"/>
@@ -25130,7 +25730,7 @@
       </c>
       <c r="AH148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI148" s="4" t="inlineStr"/>
@@ -25275,7 +25875,7 @@
       </c>
       <c r="AH149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI149" s="4" t="inlineStr"/>
@@ -25390,7 +25990,7 @@
       </c>
       <c r="AH150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI150" s="4" t="inlineStr"/>
@@ -25535,7 +26135,7 @@
       </c>
       <c r="AH151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI151" s="4" t="inlineStr"/>
@@ -25684,7 +26284,7 @@
       </c>
       <c r="AH152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI152" s="4" t="inlineStr"/>
@@ -25828,7 +26428,7 @@
       </c>
       <c r="AH153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI153" s="4" t="inlineStr"/>
@@ -25935,7 +26535,7 @@
       </c>
       <c r="AH154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI154" s="4" t="inlineStr"/>
@@ -26083,7 +26683,7 @@
       </c>
       <c r="AH155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI155" s="4" t="inlineStr"/>
@@ -26232,7 +26832,7 @@
       </c>
       <c r="AH156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI156" s="4" t="inlineStr"/>
@@ -26381,7 +26981,7 @@
       </c>
       <c r="AH157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI157" s="4" t="inlineStr"/>
@@ -26519,7 +27119,7 @@
       </c>
       <c r="AH158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI158" s="4" t="inlineStr"/>
@@ -26660,7 +27260,7 @@
       </c>
       <c r="AH159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI159" s="4" t="inlineStr"/>
@@ -26800,7 +27400,7 @@
       </c>
       <c r="AH160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI160" s="4" t="inlineStr"/>
@@ -26949,7 +27549,7 @@
       </c>
       <c r="AH161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI161" s="4" t="inlineStr"/>
@@ -27092,7 +27692,7 @@
       </c>
       <c r="AH162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI162" s="4" t="inlineStr"/>
@@ -27237,7 +27837,7 @@
       </c>
       <c r="AH163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI163" s="4" t="inlineStr"/>
@@ -27381,7 +27981,7 @@
       </c>
       <c r="AH164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI164" s="4" t="inlineStr"/>
@@ -27488,7 +28088,7 @@
       </c>
       <c r="AH165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI165" s="4" t="inlineStr"/>
@@ -27631,7 +28231,7 @@
       </c>
       <c r="AH166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI166" s="4" t="inlineStr"/>
@@ -27779,7 +28379,7 @@
       </c>
       <c r="AH167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI167" s="4" t="inlineStr"/>
@@ -27913,7 +28513,7 @@
       </c>
       <c r="AH168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI168" s="4" t="inlineStr"/>
@@ -28053,7 +28653,7 @@
       </c>
       <c r="AH169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI169" s="4" t="inlineStr"/>
@@ -28199,7 +28799,7 @@
       </c>
       <c r="AH170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI170" s="4" t="inlineStr"/>
@@ -28345,7 +28945,7 @@
       </c>
       <c r="AH171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI171" s="4" t="inlineStr"/>
@@ -28466,7 +29066,7 @@
       </c>
       <c r="AH172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI172" s="4" t="inlineStr"/>
@@ -28610,7 +29210,7 @@
       </c>
       <c r="AH173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI173" s="4" t="inlineStr"/>
@@ -28726,7 +29326,7 @@
       </c>
       <c r="AH174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI174" s="4" t="inlineStr"/>
@@ -28870,7 +29470,7 @@
       </c>
       <c r="AH175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI175" s="4" t="inlineStr"/>
@@ -29018,7 +29618,7 @@
       </c>
       <c r="AH176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI176" s="4" t="inlineStr"/>
@@ -29156,7 +29756,7 @@
       </c>
       <c r="AH177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI177" s="4" t="inlineStr"/>
@@ -29298,7 +29898,7 @@
       </c>
       <c r="AH178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI178" s="4" t="inlineStr"/>
@@ -29439,7 +30039,7 @@
       </c>
       <c r="AH179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI179" s="4" t="inlineStr"/>
@@ -29587,7 +30187,7 @@
       </c>
       <c r="AH180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI180" s="4" t="inlineStr"/>
@@ -29723,7 +30323,7 @@
       </c>
       <c r="AH181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI181" s="4" t="inlineStr"/>
@@ -29867,7 +30467,7 @@
       </c>
       <c r="AH182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI182" s="4" t="inlineStr"/>
@@ -30009,7 +30609,7 @@
       </c>
       <c r="AH183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI183" s="4" t="inlineStr"/>
@@ -30151,7 +30751,7 @@
       </c>
       <c r="AH184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI184" s="4" t="inlineStr"/>
@@ -30301,7 +30901,7 @@
       </c>
       <c r="AH185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI185" s="4" t="inlineStr"/>
@@ -30442,7 +31042,7 @@
       </c>
       <c r="AH186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI186" s="4" t="inlineStr"/>
@@ -30584,7 +31184,7 @@
       </c>
       <c r="AH187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI187" s="4" t="inlineStr"/>
@@ -30721,7 +31321,7 @@
       </c>
       <c r="AH188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI188" s="4" t="inlineStr"/>
@@ -30857,7 +31457,7 @@
       </c>
       <c r="AH189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI189" s="4" t="inlineStr"/>
@@ -31006,7 +31606,7 @@
       </c>
       <c r="AH190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI190" s="4" t="inlineStr"/>
@@ -31153,7 +31753,7 @@
       </c>
       <c r="AH191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI191" s="4" t="inlineStr"/>
@@ -31273,7 +31873,7 @@
       </c>
       <c r="AH192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI192" s="4" t="inlineStr"/>
@@ -31411,7 +32011,7 @@
       </c>
       <c r="AH193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI193" s="4" t="inlineStr"/>
@@ -31554,7 +32154,7 @@
       </c>
       <c r="AH194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI194" s="4" t="inlineStr"/>
@@ -31696,7 +32296,7 @@
       </c>
       <c r="AH195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI195" s="4" t="inlineStr"/>
@@ -31837,7 +32437,7 @@
       </c>
       <c r="AH196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI196" s="4" t="inlineStr"/>
@@ -31975,7 +32575,7 @@
       </c>
       <c r="AH197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI197" s="4" t="inlineStr"/>
@@ -32113,7 +32713,7 @@
       </c>
       <c r="AH198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI198" s="4" t="inlineStr"/>
@@ -32258,7 +32858,7 @@
       </c>
       <c r="AH199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI199" s="4" t="inlineStr"/>
@@ -32402,7 +33002,7 @@
       </c>
       <c r="AH200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI200" s="4" t="inlineStr"/>
@@ -32545,7 +33145,7 @@
       </c>
       <c r="AH201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AI201" s="4" t="inlineStr"/>
